--- a/api/clv3/xlsx/en/IATIOrganisationIdentifier.xlsx
+++ b/api/clv3/xlsx/en/IATIOrganisationIdentifier.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="162">
   <si>
     <t>code</t>
   </si>
@@ -106,6 +106,18 @@
     <t>http://www.aias.gov.mz/</t>
   </si>
   <si>
+    <t>XI-IATI-AJS</t>
+  </si>
+  <si>
+    <t>Associations des Juristes Sénégalaises (AJS)</t>
+  </si>
+  <si>
+    <t>The Association des Juristes Sénégalaises (AJS) is an association of women lawyers who promote and contribute to the protection of the rights of individuals, particularly women and children.</t>
+  </si>
+  <si>
+    <t>http://www.femmesjuristes.org</t>
+  </si>
+  <si>
     <t>XI-IATI-ATTIC</t>
   </si>
   <si>
@@ -118,6 +130,18 @@
     <t>Website is still in progress</t>
   </si>
   <si>
+    <t>XI-IATI-BBDN</t>
+  </si>
+  <si>
+    <t>Bangladesh Business &amp; Disability Network</t>
+  </si>
+  <si>
+    <t>The Bangladesh Business and Disability Network (BBDN) is a voluntary group of representatives from business, industry, employers’ organizations and selected non-governmental and disabled peoples’ organizations. BBDN has a primary purpose of facilitating disability and work place diversity in Bangladesh from the perspective of the business and human rights cases.</t>
+  </si>
+  <si>
+    <t>https://www.bbdn.com.bd/</t>
+  </si>
+  <si>
     <t>XI-IATI-EBRD</t>
   </si>
   <si>
@@ -310,6 +334,18 @@
     <t>https://www.international-climate-initiative.com/</t>
   </si>
   <si>
+    <t>XI-IATI-KHF</t>
+  </si>
+  <si>
+    <t>The King Hussein Foundation (KHF)</t>
+  </si>
+  <si>
+    <t>Their mission is to build upon King Hussein’s lifelong commitment to peace, sustainable community development and cross-cultural understanding through national and regional programs that promote education and leadership, economic empowerment and participatory decision-making.</t>
+  </si>
+  <si>
+    <t>http://www.kinghusseinfoundation.org/</t>
+  </si>
+  <si>
     <t>XI-IATI-LPI</t>
   </si>
   <si>
@@ -440,6 +476,30 @@
   </si>
   <si>
     <t>http://wash-alliance.org/</t>
+  </si>
+  <si>
+    <t>XI-IATI-WBTF</t>
+  </si>
+  <si>
+    <t>World Bank Trust Funds (WBTF)</t>
+  </si>
+  <si>
+    <t>A trust fund (TF) is a financing arrangement established with contributions from one or more external development partner(s)/partners, and in some cases, from the World Bank Group, to support development-related activities. The World Bank acts as a trustee/administrator for development partners (donors) funds and implements the activities financed through trust funds in accordance with the signed agreements with donors. As part of fiduciary obligations, the World Bank as Trustee/administrator of trust funds maintains the records for trust funds activities distinct and separate from the activities of IBRD and IDA. The Bank also provides periodic report on the financial situation and results of the individual trust funds to donors.</t>
+  </si>
+  <si>
+    <t>https://www.worldbank.org/en/publication/trust-fund-annual-report-2019</t>
+  </si>
+  <si>
+    <t>XI-IATI-WVDRC</t>
+  </si>
+  <si>
+    <t>World Vision DRC</t>
+  </si>
+  <si>
+    <t>Our teams have been working in the DRC since 1984. Today, we are working to contribute to the measurable and sustainable improvement of well-being for 5,311,208 children and their communities through transformational development and humanitarian relief programmes focused on: health and nutrition, education, water and sanitation, protecting children, livelihoods and resilience, food aid, psychosocial support and the reintegration if displaced people.</t>
+  </si>
+  <si>
+    <t>https://www.wvi.org/congo-drc/about-us</t>
   </si>
 </sst>
 </file>
@@ -784,7 +844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -916,7 +976,7 @@
       <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E8" t="s">
@@ -933,7 +993,7 @@
       <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>37</v>
       </c>
       <c r="E9" t="s">
@@ -1307,7 +1367,7 @@
       <c r="C31" t="s">
         <v>124</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>125</v>
       </c>
       <c r="E31" t="s">
@@ -1358,7 +1418,7 @@
       <c r="C34" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s">
         <v>137</v>
       </c>
       <c r="E34" t="s">
@@ -1379,6 +1439,91 @@
         <v>141</v>
       </c>
       <c r="E35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B40" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1390,7 +1535,7 @@
     <hyperlink ref="D5" r:id="rId4"/>
     <hyperlink ref="D6" r:id="rId5"/>
     <hyperlink ref="D7" r:id="rId6"/>
-    <hyperlink ref="D9" r:id="rId7"/>
+    <hyperlink ref="D8" r:id="rId7"/>
     <hyperlink ref="D10" r:id="rId8"/>
     <hyperlink ref="D11" r:id="rId9"/>
     <hyperlink ref="D12" r:id="rId10"/>
@@ -1412,10 +1557,15 @@
     <hyperlink ref="D28" r:id="rId26"/>
     <hyperlink ref="D29" r:id="rId27"/>
     <hyperlink ref="D30" r:id="rId28"/>
-    <hyperlink ref="D32" r:id="rId29"/>
-    <hyperlink ref="D33" r:id="rId30"/>
-    <hyperlink ref="D34" r:id="rId31"/>
+    <hyperlink ref="D31" r:id="rId29"/>
+    <hyperlink ref="D32" r:id="rId30"/>
+    <hyperlink ref="D33" r:id="rId31"/>
     <hyperlink ref="D35" r:id="rId32"/>
+    <hyperlink ref="D36" r:id="rId33"/>
+    <hyperlink ref="D37" r:id="rId34"/>
+    <hyperlink ref="D38" r:id="rId35"/>
+    <hyperlink ref="D39" r:id="rId36"/>
+    <hyperlink ref="D40" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
